--- a/Walking Weight and Incline Studies.xlsx
+++ b/Walking Weight and Incline Studies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33ab2cc4ec646a75/Documents/GitHub/Treadmill/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{F22A3048-84E7-4D24-9552-1420F4B3C562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2259416-EA65-4EE6-ADC6-175AEACB8F9D}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{F22A3048-84E7-4D24-9552-1420F4B3C562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E3FEDD-6627-49B0-8D2F-BCD863BC73B2}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="2610" windowWidth="21600" windowHeight="11385" xr2:uid="{F0F1F459-CD4B-4BC2-B1B7-F2EFBF52F5B6}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="17910" windowHeight="15600" xr2:uid="{F0F1F459-CD4B-4BC2-B1B7-F2EFBF52F5B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>authors</t>
   </si>
@@ -81,13 +81,103 @@
   </si>
   <si>
     <t>oxygen consumption during weighted walking is statistically different from walking in the unweighted condition for 10, 15,and 20% BW conditions at all speeds</t>
+  </si>
+  <si>
+    <t>cost units</t>
+  </si>
+  <si>
+    <t>cost measured (approx.)</t>
+  </si>
+  <si>
+    <t>make comparable</t>
+  </si>
+  <si>
+    <t>estimation based on Ludlow</t>
+  </si>
+  <si>
+    <t>participants were cued through a combination of step placement asymmetries (belts were tied) that were matched to specific speeds. Then participants were alloed to explore the controller freely before choosing a speed-asym combination to walk for 5 min (exp 1) or 1 km (exp 2)</t>
+  </si>
+  <si>
+    <t>Sombric, Calvert, Torres-Oviedo</t>
+  </si>
+  <si>
+    <t>Large propulsion demands increase locomotor adaptation at the expense of step length symmetry</t>
+  </si>
+  <si>
+    <t>not measured; assume cost is similar to tied belt walking at 1 m/s (butterfield); assume that 9 degree incline (Ludlow 2016) is very similar to 8 degree</t>
+  </si>
+  <si>
+    <t>* estimated gross metabolic cost (W / kgBW)</t>
+  </si>
+  <si>
+    <t>Selinger</t>
+  </si>
+  <si>
+    <t>gross metabolic  cost (W/kgBW)</t>
+  </si>
+  <si>
+    <t>1 m/s level walking with 17% BW added mass: 3.5 W/kgBW; inline walking at  9 degrees: 7.5 W/kgBW</t>
+  </si>
+  <si>
+    <t>gross, but with supine rest reported</t>
+  </si>
+  <si>
+    <t>using Ludlow 2016 equation: 6.76 W/ kgBW</t>
+  </si>
+  <si>
+    <t>adaptation to split-belt walking at 8.5 degree decline, level, and 8.5 degree incline with the belt speeds at 1.5 and 0.5 m/s</t>
+  </si>
+  <si>
+    <t>mine</t>
+  </si>
+  <si>
+    <t>gross metabolic cost (W/kgBW)</t>
+  </si>
+  <si>
+    <t>gross cost of locomotion (J/kg*m); power (w); pnet (W/kg)</t>
+  </si>
+  <si>
+    <t>Roemmich, Leech, Conzalez, Bastian</t>
+  </si>
+  <si>
+    <t>Trading symmetry for energy cost during walking in healthy adults and persons post-stroke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost of transport (o2 consumption / (kg * m/s) </t>
+  </si>
+  <si>
+    <t>did they measure preferred speed? Most participants chose the combination with the lowest cost of transport in both experiments, those combinations were:  1 m/s with a small limp (tied alternative was 0.5 m/s) and 1.5 m/s with a small right limp (tied alternative was 0.5 m/s)  - in both experiements participants could walk at their prefered speed if they generated a large right limp</t>
+  </si>
+  <si>
+    <t>for the 5 minute walking period: cot = ~5 J/(kg*m); for the 1 km walking period cot ~=4 J/(kg*m) at 1.5 m/s</t>
+  </si>
+  <si>
+    <t>for the 5 minutes selection: 5 W/ kg; for the 1 km selection = 6 W/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">based on tied belt data, walking at 0.5 m/s has a metabolic rate 3 W/kg - in both decisions this is lower than the metabolic cost of the chosen </t>
+  </si>
+  <si>
+    <t>Humans can continuously optimize energetic cost during walking</t>
+  </si>
+  <si>
+    <t>walked with a knee exo that penalized prefered step frequency, after exploration, participants adjusted to the new optimal step frequency</t>
+  </si>
+  <si>
+    <t>net metabolic power (W/kg</t>
+  </si>
+  <si>
+    <t>sensitivity to 0.5 N / kg</t>
+  </si>
+  <si>
+    <t>using Ludlow 2016 equation: 3.77  W/kgBW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,8 +186,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -124,10 +228,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -145,6 +256,136 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>247649</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>542924</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E4621B1-1112-358E-06F1-DBF875DCF87E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3667125" y="2133599"/>
+          <a:ext cx="3143250" cy="2524125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200"/>
+            <a:t>Units</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t> for metabolic / energy / effort costs</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t>+ Joules measure energy; watts = joules / s</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t>metabolic power</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t>cost of transport = J / (kg * distance)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+            <a:t>oxygen consumption</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,379 +705,456 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E56F6C9-43D2-4B86-8304-E8679F1DD683}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="3"/>
+    <col min="4" max="4" width="32.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" s="5" customFormat="1" ht="27" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="108" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="5">
         <v>2016</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>2005</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>2006</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="121.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2019</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="54" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2015</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>